--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122308482</v>
+        <v>122308317</v>
       </c>
       <c r="B2" t="n">
-        <v>90799</v>
+        <v>91184</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481018</v>
+        <v>481022</v>
       </c>
       <c r="R2" t="n">
-        <v>6515681</v>
+        <v>6515687</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122308317</v>
+        <v>122308232</v>
       </c>
       <c r="B3" t="n">
-        <v>91184</v>
+        <v>92055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481022</v>
+        <v>481062</v>
       </c>
       <c r="R3" t="n">
-        <v>6515687</v>
+        <v>6515700</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122308232</v>
+        <v>122308482</v>
       </c>
       <c r="B4" t="n">
-        <v>92055</v>
+        <v>90799</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481062</v>
+        <v>481018</v>
       </c>
       <c r="R4" t="n">
-        <v>6515700</v>
+        <v>6515681</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122308317</v>
+        <v>122308482</v>
       </c>
       <c r="B2" t="n">
-        <v>91184</v>
+        <v>90809</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481022</v>
+        <v>481018</v>
       </c>
       <c r="R2" t="n">
-        <v>6515687</v>
+        <v>6515681</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122308232</v>
+        <v>122308317</v>
       </c>
       <c r="B3" t="n">
-        <v>92055</v>
+        <v>91194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481062</v>
+        <v>481022</v>
       </c>
       <c r="R3" t="n">
-        <v>6515700</v>
+        <v>6515687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122308482</v>
+        <v>122308232</v>
       </c>
       <c r="B4" t="n">
-        <v>90799</v>
+        <v>92065</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481018</v>
+        <v>481062</v>
       </c>
       <c r="R4" t="n">
-        <v>6515681</v>
+        <v>6515700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122308482</v>
+        <v>122308317</v>
       </c>
       <c r="B2" t="n">
-        <v>90809</v>
+        <v>91206</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481018</v>
+        <v>481022</v>
       </c>
       <c r="R2" t="n">
-        <v>6515681</v>
+        <v>6515687</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122308317</v>
+        <v>122308482</v>
       </c>
       <c r="B3" t="n">
-        <v>91194</v>
+        <v>90821</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481022</v>
+        <v>481018</v>
       </c>
       <c r="R3" t="n">
-        <v>6515687</v>
+        <v>6515681</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>122308232</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92077</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122308317</v>
+        <v>122308482</v>
       </c>
       <c r="B2" t="n">
-        <v>91206</v>
+        <v>90828</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481022</v>
+        <v>481018</v>
       </c>
       <c r="R2" t="n">
-        <v>6515687</v>
+        <v>6515681</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122308482</v>
+        <v>122308317</v>
       </c>
       <c r="B3" t="n">
-        <v>90821</v>
+        <v>91211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481018</v>
+        <v>481022</v>
       </c>
       <c r="R3" t="n">
-        <v>6515681</v>
+        <v>6515687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>122308232</v>
       </c>
       <c r="B4" t="n">
-        <v>92077</v>
+        <v>92082</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122308482</v>
+        <v>122308317</v>
       </c>
       <c r="B2" t="n">
-        <v>90828</v>
+        <v>91216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>5420</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481018</v>
+        <v>481022</v>
       </c>
       <c r="R2" t="n">
-        <v>6515681</v>
+        <v>6515687</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122308317</v>
+        <v>122308232</v>
       </c>
       <c r="B3" t="n">
-        <v>91211</v>
+        <v>92087</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Grovticka</t>
-        </is>
+        <v>4364</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481022</v>
+        <v>481062</v>
       </c>
       <c r="R3" t="n">
-        <v>6515687</v>
+        <v>6515700</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122308232</v>
+        <v>122308482</v>
       </c>
       <c r="B4" t="n">
-        <v>92082</v>
+        <v>90833</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +901,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dropptaggsvamp</t>
-        </is>
+        <v>5442</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481062</v>
+        <v>481018</v>
       </c>
       <c r="R4" t="n">
-        <v>6515700</v>
+        <v>6515681</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308317</v>
       </c>
       <c r="B2" t="n">
-        <v>91216</v>
+        <v>91229</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>5420</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122308232</v>
+        <v>122308482</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>90846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,20 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481062</v>
+        <v>481018</v>
       </c>
       <c r="R3" t="n">
-        <v>6515700</v>
+        <v>6515681</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122308482</v>
+        <v>122308232</v>
       </c>
       <c r="B4" t="n">
-        <v>90833</v>
+        <v>92100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,20 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481018</v>
+        <v>481062</v>
       </c>
       <c r="R4" t="n">
-        <v>6515681</v>
+        <v>6515700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122308317</v>
+        <v>122308232</v>
       </c>
       <c r="B2" t="n">
-        <v>91229</v>
+        <v>92113</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481022</v>
+        <v>481062</v>
       </c>
       <c r="R2" t="n">
-        <v>6515687</v>
+        <v>6515700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>122308482</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122308232</v>
+        <v>122308317</v>
       </c>
       <c r="B4" t="n">
-        <v>92100</v>
+        <v>91242</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481062</v>
+        <v>481022</v>
       </c>
       <c r="R4" t="n">
-        <v>6515700</v>
+        <v>6515687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122308232</v>
+        <v>122308482</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>90853</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481062</v>
+        <v>481018</v>
       </c>
       <c r="R2" t="n">
-        <v>6515700</v>
+        <v>6515681</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122308482</v>
+        <v>122308317</v>
       </c>
       <c r="B3" t="n">
-        <v>90859</v>
+        <v>91243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481018</v>
+        <v>481022</v>
       </c>
       <c r="R3" t="n">
-        <v>6515681</v>
+        <v>6515687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122308317</v>
+        <v>122308232</v>
       </c>
       <c r="B4" t="n">
-        <v>91242</v>
+        <v>92114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481022</v>
+        <v>481062</v>
       </c>
       <c r="R4" t="n">
-        <v>6515687</v>
+        <v>6515700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122308482</v>
+        <v>122308232</v>
       </c>
       <c r="B2" t="n">
-        <v>90853</v>
+        <v>92114</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481018</v>
+        <v>481062</v>
       </c>
       <c r="R2" t="n">
-        <v>6515681</v>
+        <v>6515700</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122308232</v>
+        <v>122308482</v>
       </c>
       <c r="B4" t="n">
-        <v>92114</v>
+        <v>90853</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481062</v>
+        <v>481018</v>
       </c>
       <c r="R4" t="n">
-        <v>6515700</v>
+        <v>6515681</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308232</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122308317</v>
+        <v>122308482</v>
       </c>
       <c r="B3" t="n">
-        <v>91243</v>
+        <v>90854</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481022</v>
+        <v>481018</v>
       </c>
       <c r="R3" t="n">
-        <v>6515687</v>
+        <v>6515681</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122308482</v>
+        <v>122308317</v>
       </c>
       <c r="B4" t="n">
-        <v>90853</v>
+        <v>91244</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481018</v>
+        <v>481022</v>
       </c>
       <c r="R4" t="n">
-        <v>6515681</v>
+        <v>6515687</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122308232</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122308482</v>
+        <v>122308317</v>
       </c>
       <c r="B3" t="n">
-        <v>90854</v>
+        <v>91247</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481018</v>
+        <v>481022</v>
       </c>
       <c r="R3" t="n">
-        <v>6515681</v>
+        <v>6515687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122308317</v>
+        <v>122308482</v>
       </c>
       <c r="B4" t="n">
-        <v>91244</v>
+        <v>90857</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481022</v>
+        <v>481018</v>
       </c>
       <c r="R4" t="n">
-        <v>6515687</v>
+        <v>6515681</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 54877-2024 artfynd.xlsx
+++ b/artfynd/A 54877-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122308232</v>
+        <v>122308317</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>91247</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>481062</v>
+        <v>481022</v>
       </c>
       <c r="R2" t="n">
-        <v>6515700</v>
+        <v>6515687</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122308317</v>
+        <v>122308482</v>
       </c>
       <c r="B3" t="n">
-        <v>91247</v>
+        <v>90857</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>481022</v>
+        <v>481018</v>
       </c>
       <c r="R3" t="n">
-        <v>6515687</v>
+        <v>6515681</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122308482</v>
+        <v>122308232</v>
       </c>
       <c r="B4" t="n">
-        <v>90857</v>
+        <v>92118</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>481018</v>
+        <v>481062</v>
       </c>
       <c r="R4" t="n">
-        <v>6515681</v>
+        <v>6515700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
